--- a/data/trans_camb/P16A07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,41</t>
+          <t>-0,19; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,65</t>
+          <t>-0,34; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,41</t>
+          <t>-0,34; 1,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,25</t>
+          <t>-2,5; 0,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,27</t>
+          <t>-2,75; 0,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,03</t>
+          <t>-1,5; 4,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,46</t>
+          <t>-1,17; 0,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,34</t>
+          <t>-1,26; 0,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,99</t>
+          <t>-0,82; 1,78</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,87</t>
+          <t>-92,21; 67,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,45</t>
+          <t>-100,0; 62,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,52; 440,68</t>
+          <t>-70,91; 363,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,9; 105,31</t>
+          <t>-83,25; 120,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 75,27</t>
+          <t>-84,73; 89,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,68; 381,09</t>
+          <t>-69,37; 299,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,66</t>
+          <t>-0,8; 1,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,99</t>
+          <t>-1,18; 1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,52</t>
+          <t>-1,7; 0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,32</t>
+          <t>-1,99; 2,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,86</t>
+          <t>-2,93; 0,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,96</t>
+          <t>-2,69; 1,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,41</t>
+          <t>-1,03; 1,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,52</t>
+          <t>-1,61; 0,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,95</t>
+          <t>-1,51; 0,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 233,51</t>
+          <t>-51,95; 298,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,64; 173,9</t>
+          <t>-71,69; 154,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,38; 118,42</t>
+          <t>-97,5; 150,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 115,27</t>
+          <t>-48,9; 116,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 44,15</t>
+          <t>-70,21; 53,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 89,46</t>
+          <t>-63,3; 85,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 85,75</t>
+          <t>-39,64; 94,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,81; 35,54</t>
+          <t>-59,78; 36,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 61,74</t>
+          <t>-58,34; 61,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,99</t>
+          <t>-0,93; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,56</t>
+          <t>-1,71; 1,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,37</t>
+          <t>-1,19; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,62</t>
+          <t>1,55; 6,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,47</t>
+          <t>-1,39; 2,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,88</t>
+          <t>-1,32; 2,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,32</t>
+          <t>1,03; 4,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,63</t>
+          <t>-1,15; 1,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,15</t>
+          <t>-0,7; 2,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 229,09</t>
+          <t>-31,84; 213,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,35; 128,45</t>
+          <t>-58,5; 119,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 179,83</t>
+          <t>-45,03; 191,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 230,29</t>
+          <t>26,35; 230,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 91,03</t>
+          <t>-32,54; 96,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 110,76</t>
+          <t>-27,09; 98,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,32; 194,83</t>
+          <t>26,98; 176,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 73,24</t>
+          <t>-31,51; 59,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 95,43</t>
+          <t>-20,95; 83,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,37</t>
+          <t>-1,07; 3,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,08</t>
+          <t>-1,52; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,1</t>
+          <t>-1,36; 4,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,86</t>
+          <t>-3,0; 3,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,89</t>
+          <t>-3,78; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,97</t>
+          <t>-4,48; 1,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,75</t>
+          <t>-1,31; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,92</t>
+          <t>-1,82; 1,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,16</t>
+          <t>-2,54; 2,19</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 250,47</t>
+          <t>-36,94; 224,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 151,49</t>
+          <t>-48,83; 140,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 265,44</t>
+          <t>-38,6; 261,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 59,62</t>
+          <t>-27,88; 53,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 38,75</t>
+          <t>-35,07; 45,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 27,11</t>
+          <t>-38,3; 25,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 59,65</t>
+          <t>-19,9; 63,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 43,75</t>
+          <t>-28,11; 43,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,86; 42,38</t>
+          <t>-38,06; 43,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,18</t>
+          <t>-0,74; 5,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,92</t>
+          <t>-1,99; 3,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,07</t>
+          <t>-0,37; 4,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 8,01</t>
+          <t>-1,77; 8,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,42</t>
+          <t>-6,15; 3,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,47</t>
+          <t>-3,88; 3,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,84</t>
+          <t>-0,23; 5,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,06</t>
+          <t>-2,99; 2,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,3</t>
+          <t>-1,27; 3,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 216,38</t>
+          <t>-17,06; 248,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 118,04</t>
+          <t>-43,39; 157,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 210,78</t>
+          <t>-8,72; 206,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 78,58</t>
+          <t>-12,36; 81,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 35,67</t>
+          <t>-38,85; 31,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 33,93</t>
+          <t>-25,76; 40,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 86,77</t>
+          <t>-3,35; 79,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 31,08</t>
+          <t>-31,59; 34,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 48,17</t>
+          <t>-13,56; 48,13</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,07</t>
+          <t>-2,48; 3,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,68</t>
+          <t>-4,65; 0,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,76</t>
+          <t>-4,0; 0,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 7,33</t>
+          <t>-1,79; 7,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,77</t>
+          <t>-1,39; 8,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 3,27</t>
+          <t>-8,79; 2,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,67</t>
+          <t>-0,94; 4,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,87</t>
+          <t>-1,99; 3,59</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 1,1</t>
+          <t>-5,39; 1,2</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 186,95</t>
+          <t>-51,48; 188,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-81,41; 42,17</t>
+          <t>-83,23; 37,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,08; 36,78</t>
+          <t>-71,22; 48,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 91,3</t>
+          <t>-14,82; 89,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 97,05</t>
+          <t>-10,17; 106,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 37,15</t>
+          <t>-67,55; 33,17</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 75,33</t>
+          <t>-11,83; 85,28</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 64,19</t>
+          <t>-22,56; 63,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 17,12</t>
+          <t>-62,2; 16,98</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,2</t>
+          <t>-3,0; 5,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,84</t>
+          <t>-4,85; 2,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,89</t>
+          <t>-2,45; 4,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 6,16</t>
+          <t>-3,04; 6,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,39</t>
+          <t>-3,23; 6,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,09</t>
+          <t>-3,83; 4,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,28</t>
+          <t>-1,92; 4,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,02</t>
+          <t>-2,18; 4,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,29</t>
+          <t>-2,34; 3,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 186,48</t>
+          <t>-49,39; 205,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,76; 123,31</t>
+          <t>-65,46; 120,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 207,4</t>
+          <t>-38,64; 207,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 86,15</t>
+          <t>-24,24; 86,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 108,29</t>
+          <t>-27,4; 85,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 58,53</t>
+          <t>-29,89; 58,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 67,32</t>
+          <t>-21,77; 75,91</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 65,17</t>
+          <t>-23,35; 71,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 55,99</t>
+          <t>-24,57; 55,62</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,93</t>
+          <t>0,24; 1,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,68</t>
+          <t>-0,59; 0,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,88</t>
+          <t>0,26; 1,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,07</t>
+          <t>0,67; 3,26</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,77</t>
+          <t>-0,56; 1,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,85</t>
+          <t>-0,9; 1,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,31</t>
+          <t>0,71; 2,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,09</t>
+          <t>-0,36; 1,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,71</t>
+          <t>0,1; 1,67</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5,48; 102,5</t>
+          <t>9,23; 105,17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 37,1</t>
+          <t>-24,77; 44,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7,85; 104,67</t>
+          <t>9,6; 110,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,83; 52,1</t>
+          <t>9,15; 56,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 29,55</t>
+          <t>-7,99; 32,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 31,16</t>
+          <t>-12,2; 31,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,21; 57,59</t>
+          <t>15,34; 56,44</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 27,41</t>
+          <t>-8,22; 26,14</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2,42; 43,0</t>
+          <t>2,14; 41,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,55</t>
+          <t>-0,19; 1,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,44</t>
+          <t>-0,28; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,63</t>
+          <t>-0,19; 2,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,23</t>
+          <t>-2,6; 0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,25</t>
+          <t>-2,49; 0,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,31</t>
+          <t>-1,6; 3,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,5</t>
+          <t>-1,15; 0,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,43</t>
+          <t>-1,22; 0,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,78</t>
+          <t>-0,63; 2,06</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>276,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-92,21; 67,93</t>
+          <t>-100,0; 49,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,7</t>
+          <t>-100,0; 51,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 363,33</t>
+          <t>-73,55; 326,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,25; 120,89</t>
+          <t>-83,11; 98,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,73; 89,89</t>
+          <t>-85,31; 83,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,37; 299,75</t>
+          <t>-57,51; 310,52</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,82</t>
+          <t>-0,85; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,03</t>
+          <t>-1,33; 0,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,5</t>
+          <t>-1,49; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,32</t>
+          <t>-1,88; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,82</t>
+          <t>-2,93; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,79</t>
+          <t>-2,42; 1,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,38</t>
+          <t>-0,94; 1,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,52</t>
+          <t>-1,71; 0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,89</t>
+          <t>-1,38; 1,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-55,51%</t>
+          <t>-30,01%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,68%</t>
+          <t>-10,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,13%</t>
+          <t>-11,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,95; 298,65</t>
+          <t>-55,03; 267,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 154,99</t>
+          <t>-75,68; 170,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-97,5; 150,87</t>
+          <t>-94,7; 177,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 116,06</t>
+          <t>-50,06; 108,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 53,45</t>
+          <t>-69,22; 42,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 85,91</t>
+          <t>-59,53; 89,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,64; 94,71</t>
+          <t>-36,65; 93,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 36,32</t>
+          <t>-63,86; 29,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 61,37</t>
+          <t>-54,17; 66,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,98</t>
+          <t>-0,74; 3,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,53</t>
+          <t>-1,66; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,5</t>
+          <t>-1,49; 2,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,72</t>
+          <t>1,7; 7,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,57</t>
+          <t>-1,67; 2,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,65</t>
+          <t>-1,33; 2,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,25</t>
+          <t>1,12; 4,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,43</t>
+          <t>-1,21; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,01</t>
+          <t>-0,88; 1,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 213,84</t>
+          <t>-30,27; 221,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 119,57</t>
+          <t>-54,82; 110,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 191,34</t>
+          <t>-53,03; 152,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,35; 230,16</t>
+          <t>29,59; 262,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 96,5</t>
+          <t>-34,89; 91,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 98,97</t>
+          <t>-27,33; 104,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,98; 176,66</t>
+          <t>31,95; 181,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 59,61</t>
+          <t>-32,68; 60,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 83,18</t>
+          <t>-24,08; 80,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,2</t>
+          <t>-1,03; 3,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,88</t>
+          <t>-1,76; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,07</t>
+          <t>0,95; 5,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,83</t>
+          <t>-3,13; 3,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,28</t>
+          <t>-3,66; 2,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,79</t>
+          <t>-3,89; 2,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,8</t>
+          <t>-1,35; 2,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,96</t>
+          <t>-2,0; 1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,19</t>
+          <t>-0,59; 3,0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>136,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,31%</t>
+          <t>-6,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 224,34</t>
+          <t>-35,55; 251,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 140,35</t>
+          <t>-52,43; 140,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 261,29</t>
+          <t>25,36; 381,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 53,94</t>
+          <t>-28,81; 54,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 45,75</t>
+          <t>-34,54; 42,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 25,3</t>
+          <t>-34,8; 28,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 63,46</t>
+          <t>-20,1; 60,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 43,28</t>
+          <t>-29,65; 40,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 43,52</t>
+          <t>-9,01; 64,18</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,32</t>
+          <t>-0,58; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,28</t>
+          <t>-2,09; 2,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,67</t>
+          <t>-0,39; 4,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 8,24</t>
+          <t>-1,24; 8,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,19</t>
+          <t>-6,1; 2,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,86</t>
+          <t>-4,25; 3,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 5,6</t>
+          <t>0,09; 5,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,28</t>
+          <t>-3,25; 2,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,19</t>
+          <t>-1,57; 3,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 248,09</t>
+          <t>-16,11; 202,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 157,39</t>
+          <t>-47,54; 132,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 206,4</t>
+          <t>-10,06; 221,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 81,43</t>
+          <t>-9,74; 80,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 31,16</t>
+          <t>-41,23; 29,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 40,03</t>
+          <t>-26,8; 37,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 79,8</t>
+          <t>0,59; 83,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 34,18</t>
+          <t>-34,17; 32,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 48,13</t>
+          <t>-15,71; 50,06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,98</t>
+          <t>-2,72; 4,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,49</t>
+          <t>-4,66; 0,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,94</t>
+          <t>-4,09; 0,82</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,53</t>
+          <t>-1,78; 7,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 8,3</t>
+          <t>-1,46; 8,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 2,92</t>
+          <t>-2,63; 5,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,96</t>
+          <t>-1,08; 4,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,59</t>
+          <t>-1,86; 3,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 1,2</t>
+          <t>-2,39; 2,24</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-36,52%</t>
+          <t>-37,51%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-22,46%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-19,44%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 188,66</t>
+          <t>-51,67; 182,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 37,52</t>
+          <t>-81,82; 39,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 48,17</t>
+          <t>-73,47; 44,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 89,14</t>
+          <t>-15,4; 93,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 106,84</t>
+          <t>-12,7; 107,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,55; 33,17</t>
+          <t>-19,06; 75,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 85,28</t>
+          <t>-13,29; 75,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 63,01</t>
+          <t>-22,84; 60,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 16,98</t>
+          <t>-27,49; 41,48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,82</t>
+          <t>-3,37; 4,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,82</t>
+          <t>-4,78; 2,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,95</t>
+          <t>-2,77; 4,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,36</t>
+          <t>-3,14; 6,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,82</t>
+          <t>-2,58; 7,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,03</t>
+          <t>-4,07; 4,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,79</t>
+          <t>-2,53; 4,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,47</t>
+          <t>-2,59; 4,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,31</t>
+          <t>-2,91; 3,14</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,39; 205,95</t>
+          <t>-52,69; 186,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 120,97</t>
+          <t>-66,33; 112,78</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 207,95</t>
+          <t>-37,08; 163,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 86,74</t>
+          <t>-27,09; 88,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 85,88</t>
+          <t>-22,38; 97,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 58,42</t>
+          <t>-31,22; 59,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 75,91</t>
+          <t>-27,46; 69,77</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 71,58</t>
+          <t>-26,85; 68,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 55,62</t>
+          <t>-28,29; 52,4</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,87</t>
+          <t>0,16; 1,83</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,81</t>
+          <t>-0,63; 0,75</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,95</t>
+          <t>0,48; 2,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,26</t>
+          <t>0,64; 3,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,98</t>
+          <t>-0,59; 1,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,87</t>
+          <t>0,01; 2,37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,21</t>
+          <t>0,67; 2,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,05</t>
+          <t>-0,27; 1,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,67</t>
+          <t>0,58; 1,89</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>9,23; 105,17</t>
+          <t>4,37; 99,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 44,99</t>
+          <t>-26,38; 43,5</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9,6; 110,28</t>
+          <t>17,06; 113,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9,15; 56,31</t>
+          <t>8,78; 55,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 32,64</t>
+          <t>-8,42; 32,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 31,9</t>
+          <t>0,31; 41,59</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,34; 56,44</t>
+          <t>14,81; 56,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 26,14</t>
+          <t>-5,81; 29,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2,14; 41,75</t>
+          <t>11,7; 46,62</t>
         </is>
       </c>
     </row>
